--- a/Configs/GameConfig/Datas/fg/#BuildingPort-建筑端口.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingPort-建筑端口.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>kind</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +494,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -524,6 +534,11 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>in=输入,out=输出</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>物流角色:store=家园存量的输入/输出口,none=还没有收发物品的配方(FG3-LOG-03)</t>
         </is>
       </c>
     </row>
@@ -555,6 +570,11 @@
           <t>in</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -584,6 +604,11 @@
           <t>in</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -613,6 +638,11 @@
           <t>out</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -642,6 +672,11 @@
           <t>in</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -671,6 +706,11 @@
           <t>out</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -700,6 +740,11 @@
           <t>in</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -727,6 +772,11 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>in</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#BuildingPort-建筑端口.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingPort-建筑端口.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>物流角色:store=家园存量的输入/输出口,none=还没有收发物品的配方(FG3-LOG-03)</t>
+          <t>物流角色:store=家园存量的输入/输出口,none=还没有收发物品的配方(FG3-LOG-03),prod=生产建筑自己的输入/输出缓存(FG4-ECO-02)</t>
         </is>
       </c>
     </row>
@@ -777,6 +777,210 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>recycler.in0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>recycler</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>recycler.out0</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>recycler</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>extraction_drill.out0</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>extraction_drill</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>refinery_furnace.in0</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>refinery_furnace</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>refinery_furnace.out0</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>refinery_furnace</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>blending_station.in0</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>blending_station</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>prod</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#BuildingPort-建筑端口.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingPort-建筑端口.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,7 +674,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>prod</t>
         </is>
       </c>
     </row>
@@ -979,6 +979,312 @@
         </is>
       </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>parts_workshop.in0</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>parts_workshop</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>parts_workshop.out0</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>parts_workshop</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>electronics_bench.in0</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>electronics_bench</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>electronics_bench.in1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>electronics_bench</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>electronics_bench.out0</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>electronics_bench</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>component_workshop.in0</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>component_workshop</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>component_workshop.in1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>component_workshop</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>component_workshop.out0</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>component_workshop</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>firmware_burner.in0</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>firmware_burner</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>prod</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#BuildingPort-建筑端口.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingPort-建筑端口.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>prod</t>
         </is>
       </c>
     </row>
